--- a/accountant-skill/data/Jan2026/chart_of_accounts.xlsx
+++ b/accountant-skill/data/Jan2026/chart_of_accounts.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart of Accounts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1620,11 +1620,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>53000</v>
+        <v>50300</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Direct Labor Wages</t>
+          <t>Opening Work-in-Progress</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Production Overhead Costs</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1650,11 +1650,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>53100</v>
+        <v>50310</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Machine Maintenance &amp; Repair Expense</t>
+          <t>Closing Work-in-Progress</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Production Overhead Costs</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1680,11 +1680,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>53200</v>
+        <v>50320</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Production Utilities (Electricity &amp; Water)</t>
+          <t>Direct Materials Used</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Production Overhead Costs</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1710,11 +1710,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>53300</v>
+        <v>50330</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Depreciation Expenses - COGS</t>
+          <t>Direct Labor Transferred to WIP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Production Overhead Costs</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1740,11 +1740,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>60000</v>
+        <v>50340</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marketing &amp; Advertising Expense</t>
+          <t>Manufacturing Overhead Applied</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1770,11 +1770,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>61000</v>
+        <v>50350</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Office Salaries</t>
+          <t>WIP Transferred to Finished Goods</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1800,11 +1800,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>62000</v>
+        <v>53000</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Meal Allowance Expense</t>
+          <t>Direct Labor Wages</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Production Overhead Costs</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1830,11 +1830,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>63000</v>
+        <v>53100</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Utilities (Electricity &amp; Water)</t>
+          <t>Machine Maintenance &amp; Repair Expense</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Production Overhead Costs</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1860,11 +1860,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>64000</v>
+        <v>53200</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Transportation &amp; Distribution Expense</t>
+          <t>Production Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Production Overhead Costs</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1890,11 +1890,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>65000</v>
+        <v>53300</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+          <t>Depreciation Expenses - COGS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Production Overhead Costs</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1920,11 +1920,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>66000</v>
+        <v>60000</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Depreciation Expenses - SG&amp;A</t>
+          <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1950,11 +1950,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>67000</v>
+        <v>61000</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Inventory Write-off</t>
+          <t>Office Salaries</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1980,11 +1980,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>68000</v>
+        <v>62000</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Meal Allowance Expense</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2010,11 +2010,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>69000</v>
+        <v>63000</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Key Managment Personnel and Director Compensation</t>
+          <t>Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2040,29 +2040,209 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
+        <v>64000</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Distribution Expense</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>65000</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>66000</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Depreciation Expenses - SG&amp;A</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>67000</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Inventory Write-off</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>68000</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>69000</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Key Managment Personnel and Director Compensation</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
         <v>70000</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
